--- a/Data/Lambayeque/noticias_lambayeque_20261012_20261019.xlsx
+++ b/Data/Lambayeque/noticias_lambayeque_20261012_20261019.xlsx
@@ -462,35 +462,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Andina</t>
+          <t>El Comercio</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>El Niño:Midagri lideró segunda sesión multisectorial para reforzar preparación y respuesta</t>
+          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la región de Lambayeque</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Durante la sesión, se aprobó la distribución de responsabilidades territoriales entre los ministros para fortalecer la coordinación y atención de posibles emergencias en las regiones priorizadas.
-Con el objetivo de fortalecer la capacidad de respuesta del Estado, participaron los ministros de Economía y Finanzas, Vivienda, Construcción y Saneamiento, Defensa, Salud y Transportes y Comunicaciones.
-Asimismo, estuvieron presentes representantes de la Autoridad Nacional del Agua (ANA), que ejerce la secretaría técnica de la comisión, y del Instituto Nacional de Defensa Civil (Indeci).
-Durante la reunión se revisó el más reciente comunicado de la Comisión Multisectorial encargada del Estudio Nacional del Fenómeno El Niño (ENFEN) , así como sus pronósticos sobre la evolución de este evento climático.
-También se informó sobre la incorporación de los ministerios de Transportes y Comunicaciones y de Salud a la comisión.
-Coordinación multisectorial Como parte de la organización para atender posibles emergencias, se aprobó la distribución territorial de responsabilidades entre los ministros.
-De acuerdo con este acuerdo, el ministro de Defensa tendrá a su cargo la coordinación en Tumbes y Piura ; el ministro de Transportes y Comunicaciones , en Lambayeque ; el ministro de Desarrollo Agrario y Riego , en La Libertad ; y el ministro de Salud , en Áncash.
-Asimismo, los ministros de Desarrollo Agrario y Riego y de Economía y Finanzas coordinarán conjuntamente las acciones en Lima , mientras que el ministro de Vivienda, Construcción y Saneamiento tendrá a su cargo las regiones de Ica y Arequipa .
-“ De esta manera trabajaremos de forma coordinada para poder responder rápidamente ante una emergencia.
-No paramos, aquí en el Ministerio de Desarrollo Agrario trabajamos 24 por 7 para poder enfrentar de mejor manera el Fenómeno El Niño”, señaló el ministro Marco Vinelli.
-Durante la reunión también se revisaron los avances de las intervenciones en marcha y las acciones que desarrollarán los sectores, de acuerdo con sus competencias, para atender posibles emergencias y proteger a la población, la infraestructura y las actividades productivas.</t>
+          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Lambayeque, según el conteo oficial de la ONPE al 99.47% , arroja el siguiente resultado (actualizado el 19/10/2026, a las 08:15.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://andina.pe/agencia/noticia-el-ninomidagri-lidero-segunda-sesion-multisectorial-para-reforzar-preparacion-y-respuesta-1096398.aspx</t>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-region-de-lambayeque-noticia/</t>
         </is>
       </c>
     </row>
@@ -501,21 +491,21 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Resultados ONPE en región Lambayeque al 99.246 %: aquí el conteo oficial de las Elecciones Regionales y Municipales 2026</t>
+          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Lambayeque (Lambayeque)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>El domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios iniciaron a las 7 a.m. y duraron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los ciudadanos elegidos miembros de mesa (tres titulares y seis suplentes) asistieron a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los que cumplieron con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). La votación en región Lambayeque según la ONPE: ¿Cuál es la multa por no votar? Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. ¿Debo pagar multa si no cumplo con mi función de miembro de mesa? Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Lambayeque, según el conteo oficial de la ONPE al 98.546% , arroja el siguiente resultado (actualizado el 19/10/2026, a las 08:20.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/elecciones/resultados-en-lambayeque-de-las-elecciones-regionales-y-municipales-2026-segun-conteo-oficial-de-la-onpe-erm-2026-noticia/</t>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-lambayeque-lambayeque-noticia/</t>
         </is>
       </c>
     </row>
@@ -526,7 +516,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -535,7 +525,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Chiclayo, según el conteo oficial de la ONPE al 98.321% , arroja el siguiente resultado (actualizado el 17/10/2026, a las 17:20.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Chiclayo, según el conteo oficial de la ONPE al 98.573% , arroja el siguiente resultado (actualizado el 19/10/2026, a las 08:20.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -547,82 +537,18 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>El Comercio</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la región de Lambayeque</t>
+          <t>ExpoAmazónica Ucayali 2026:conoce la oferta productiva y turística de la región anfitriona</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Lambayeque, según el conteo oficial de la ONPE al 99.246% , arroja el siguiente resultado (actualizado el 17/10/2026, a las 18:26.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-region-de-lambayeque-noticia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>46312</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Más de 3.3 millones podrán votar en elecciones de centros poblados el 1 de noviembre</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Para este proceso, e l Registro Nacional de Identificación y Estado Civil (Reniec) remitió 3,398 padrones electorales a 180 municipalidades provinciales, correspondientes a un total de 3 millones 382,774 electores.
-Los ciudadanos deberán acudir a votar portando únicamente su Documento Nacional de Identidad (DNI), indispensable para acreditar su identidad durante la jornada electoral.
-Estos comicios permitirán elegir a las autoridades de 3,398 municipalidades de centros poblados, de acuerdo con la Ley Orgánica de Municipalidades.
-En cada localidad se elegirá a un alcalde y cinco regidores, quienes tendrán la responsabilidad de representar a sus comunidades y contribuir a la atención de sus principales necesidades.
-Lee también: Estas son las normas legales más importantes del viernes 16 de octubre de 2026 Entre las regiones con mayor cantidad de ciudadanos habilitados para votar destaca Cajamarca con 503,681 electores, seguida de La Libertad con 294,717; Puno con 279,951; y Piura con 270,529.
-También registran importantes cifras Huánuco (248,540), Cusco (207,051), Áncash (205,231), San Martín (177,532), Junín (161,999), Huancavelica (159,086), Apurímac (142,786), Ayacucho (135,624), y Amazonas (116,894).
-En tanto, Lambayeque cuenta con 93,276 electores; Lima, con 69,064; Loreto, con 68,984; Pasco con 64,842; Ucayali con 41,063; Tumbes con 36,818; y Arequipa con 34,288.
-Las regiones con menor número de ciudadanos convocados son Ica (7,388), Tacna (9,738), Madre de Dios (24,353) y Moquegua (29,339).
-El Reniec informó que, por primera vez, tuvo a su cargo la elaboración de los padrones electorales para las Elecciones de Autoridades de Municipalidades de Centros Poblados 2026, labor que desarrolló a escala nacional y en coordinación permanente con las municipalidades provinciales.
-Pare ello utilizó las listas de electores remitidas por las municipalidades provinciales, la información cartográfica del Registro Nacional de Municipalidades (Renamu) y las listas proporcionadas por las municipalidades de centros poblados.
-Este trabajo constituyó una etapa fundamental para contribuir a la transparencia, legitimidad y adecuada organización del proceso electoral.
-El Reniec realizó una primera entrega de los padrones electorales a las municipalidades provinciales el 19 de febrero de 2026.
-Recibió, posteriormente, solicitudes de actualización de las listas de votantes, por lo que se amplió el plazo para presentar estos pedidos y efectuar una nueva entrega de los padrones, con el propósito de contribuir al adecuado desarrollo de las elecciones.
-De acuerdo con la Ley 28440, Ley de Elecciones de Autoridades de Municipalidades de Centros Poblados, la organización de estos comicios está a cargo de las municipalidades provinciales, en coordinación con las municipalidades distritales correspondientes y con el apoyo de los organismos del sistema electoral.
-Más en Andina La presidenta de la república, Keiko Fujimori, hizo hoy una invocación para apoyar el trabajo que viene realizando el Gobierno y las demás instituciones para enfrentar las posibles consecuencias que pueda ocasionar la presencia del fenómeno El Niño??https://t.co/wLUGsPiKA1 https://t.co/e8t2bpRsAY (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 15, 2026</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-mas-33-millones-podran-votar-elecciones-centros-poblados-1-noviembre-1096152.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>46312</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ExpoAmazónica Ucayali 2026:conoce la oferta productiva y turística de la región anfitriona</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
         <is>
           <t>Este gran encuentro, oficializado por la Mancomunidad Regional Amazónica , busca fortalecer la articulación entre las regiones amazónicas, generar oportunidades para productores y emprendedores, y promover el desarrollo económico de la Amazonía.
 Entre sus actividades más destacadas están la II Expo Indígena y el VII Congreso de Emprendedores Amazónicos .
@@ -748,9 +674,69 @@
 Otra opción es llegar por vía terrestre, atravesando el centro del Perú por la Carretera Central en un viaje cuya duración es de aproximadamente 16 horas.</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-expoamazonica-ucayali-2026conoce-oferta-productiva-y-turistica-de-region-anfitriona-1096213.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>46313</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>El Niño:Midagri lideró segunda sesión multisectorial para reforzar preparación y respuesta</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Durante la sesión, se aprobó la distribución de responsabilidades territoriales entre los ministros para fortalecer la coordinación y atención de posibles emergencias en las regiones priorizadas.
+Con el objetivo de fortalecer la capacidad de respuesta del Estado, participaron los ministros de Economía y Finanzas, Vivienda, Construcción y Saneamiento, Defensa, Salud y Transportes y Comunicaciones.
+Asimismo, estuvieron presentes representantes de la Autoridad Nacional del Agua (ANA), que ejerce la secretaría técnica de la comisión, y del Instituto Nacional de Defensa Civil (Indeci).
+Durante la reunión se revisó el más reciente comunicado de la Comisión Multisectorial encargada del Estudio Nacional del Fenómeno El Niño (ENFEN) , así como sus pronósticos sobre la evolución de este evento climático.
+También se informó sobre la incorporación de los ministerios de Transportes y Comunicaciones y de Salud a la comisión.
+Coordinación multisectorial Como parte de la organización para atender posibles emergencias, se aprobó la distribución territorial de responsabilidades entre los ministros.
+De acuerdo con este acuerdo, el ministro de Defensa tendrá a su cargo la coordinación en Tumbes y Piura ; el ministro de Transportes y Comunicaciones , en Lambayeque ; el ministro de Desarrollo Agrario y Riego , en La Libertad ; y el ministro de Salud , en Áncash.
+Asimismo, los ministros de Desarrollo Agrario y Riego y de Economía y Finanzas coordinarán conjuntamente las acciones en Lima , mientras que el ministro de Vivienda, Construcción y Saneamiento tendrá a su cargo las regiones de Ica y Arequipa .
+“ De esta manera trabajaremos de forma coordinada para poder responder rápidamente ante una emergencia.
+No paramos, aquí en el Ministerio de Desarrollo Agrario trabajamos 24 por 7 para poder enfrentar de mejor manera el Fenómeno El Niño”, señaló el ministro Marco Vinelli.
+Durante la reunión también se revisaron los avances de las intervenciones en marcha y las acciones que desarrollarán los sectores, de acuerdo con sus competencias, para atender posibles emergencias y proteger a la población, la infraestructura y las actividades productivas.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-el-ninomidagri-lidero-segunda-sesion-multisectorial-para-reforzar-preparacion-y-respuesta-1096398.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>46313</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Resultados ONPE en región Lambayeque al 99.246 %: aquí el conteo oficial de las Elecciones Regionales y Municipales 2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>El domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios iniciaron a las 7 a.m. y duraron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los ciudadanos elegidos miembros de mesa (tres titulares y seis suplentes) asistieron a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los que cumplieron con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). La votación en región Lambayeque según la ONPE: ¿Cuál es la multa por no votar? Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. ¿Debo pagar multa si no cumplo con mi función de miembro de mesa? Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://andina.pe/agencia/noticia-expoamazonica-ucayali-2026conoce-oferta-productiva-y-turistica-de-region-anfitriona-1096213.aspx</t>
+          <t>https://elcomercio.pe/elecciones/resultados-en-lambayeque-de-las-elecciones-regionales-y-municipales-2026-segun-conteo-oficial-de-la-onpe-erm-2026-noticia/</t>
         </is>
       </c>
     </row>
@@ -761,14 +747,53 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
+        <v>46312</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Más de 3.3 millones podrán votar en elecciones de centros poblados el 1 de noviembre</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Para este proceso, e l Registro Nacional de Identificación y Estado Civil (Reniec) remitió 3,398 padrones electorales a 180 municipalidades provinciales, correspondientes a un total de 3 millones 382,774 electores.
+Los ciudadanos deberán acudir a votar portando únicamente su Documento Nacional de Identidad (DNI), indispensable para acreditar su identidad durante la jornada electoral.
+Estos comicios permitirán elegir a las autoridades de 3,398 municipalidades de centros poblados, de acuerdo con la Ley Orgánica de Municipalidades.
+En cada localidad se elegirá a un alcalde y cinco regidores, quienes tendrán la responsabilidad de representar a sus comunidades y contribuir a la atención de sus principales necesidades.
+Lee también: Estas son las normas legales más importantes del viernes 16 de octubre de 2026 Entre las regiones con mayor cantidad de ciudadanos habilitados para votar destaca Cajamarca con 503,681 electores, seguida de La Libertad con 294,717; Puno con 279,951; y Piura con 270,529.
+También registran importantes cifras Huánuco (248,540), Cusco (207,051), Áncash (205,231), San Martín (177,532), Junín (161,999), Huancavelica (159,086), Apurímac (142,786), Ayacucho (135,624), y Amazonas (116,894).
+En tanto, Lambayeque cuenta con 93,276 electores; Lima, con 69,064; Loreto, con 68,984; Pasco con 64,842; Ucayali con 41,063; Tumbes con 36,818; y Arequipa con 34,288.
+Las regiones con menor número de ciudadanos convocados son Ica (7,388), Tacna (9,738), Madre de Dios (24,353) y Moquegua (29,339).
+El Reniec informó que, por primera vez, tuvo a su cargo la elaboración de los padrones electorales para las Elecciones de Autoridades de Municipalidades de Centros Poblados 2026, labor que desarrolló a escala nacional y en coordinación permanente con las municipalidades provinciales.
+Pare ello utilizó las listas de electores remitidas por las municipalidades provinciales, la información cartográfica del Registro Nacional de Municipalidades (Renamu) y las listas proporcionadas por las municipalidades de centros poblados.
+Este trabajo constituyó una etapa fundamental para contribuir a la transparencia, legitimidad y adecuada organización del proceso electoral.
+El Reniec realizó una primera entrega de los padrones electorales a las municipalidades provinciales el 19 de febrero de 2026.
+Recibió, posteriormente, solicitudes de actualización de las listas de votantes, por lo que se amplió el plazo para presentar estos pedidos y efectuar una nueva entrega de los padrones, con el propósito de contribuir al adecuado desarrollo de las elecciones.
+De acuerdo con la Ley 28440, Ley de Elecciones de Autoridades de Municipalidades de Centros Poblados, la organización de estos comicios está a cargo de las municipalidades provinciales, en coordinación con las municipalidades distritales correspondientes y con el apoyo de los organismos del sistema electoral.
+Más en Andina La presidenta de la república, Keiko Fujimori, hizo hoy una invocación para apoyar el trabajo que viene realizando el Gobierno y las demás instituciones para enfrentar las posibles consecuencias que pueda ocasionar la presencia del fenómeno El Niño??https://t.co/wLUGsPiKA1 https://t.co/e8t2bpRsAY (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 15, 2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-mas-33-millones-podran-votar-elecciones-centros-poblados-1-noviembre-1096152.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
         <v>46311</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Cusco: condenan a agricultor que provocó incendio forestal que arrasó con pastos y bosques</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>El pasado 12 de octubre se activó el siniestro en el sector de Quellosesayoc, del distrito de Ancahuasi Anta, el cual, según las investigaciones de la Fiscalía Especializada en Materia Ambiental (FEMA) fue provocado por la quema de maleza.
 Lea también: Cusco: fallece poblador de Acomayo y cifra de víctimas por incendios forestales sube a 7 El agricultor no tomó las medidas de seguridad en su parcela pese a los vientos de la época, no construyó cortafuegos, y el fuego se salió de control y se propagó rápidamente devastando siete hectáreas de bosques de eucalipto y pino, así como pastos naturales y biodiversidad.
@@ -782,34 +807,9 @@
 https://t.co/TyGPYN19qL (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 16, 2026</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-cusco-condenan-a-agricultor-provoco-incendio-forestal-arraso-pastos-y-bosques-1096178.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Lambayeque (Lambayeque)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Lambayeque, según el conteo oficial de la ONPE al 98.21% , arroja el siguiente resultado (actualizado el 16/10/2026, a las 19:20.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-lambayeque-lambayeque-noticia/</t>
         </is>
       </c>
     </row>
